--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:34:41+00:00</t>
+    <t>2026-09-17T13:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:31:08+00:00</t>
+    <t>2026-10-12T16:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -897,11 +897,11 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:type}
-</t>
-  </si>
-  <si>
-    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>value:type}
+value:system}</t>
+  </si>
+  <si>
+    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.) et le system, nécessaire pour distinguer NSS-NIR de NSS-NIA qui partagent le même type (NH)</t>
   </si>
   <si>
     <t>id</t>
@@ -2812,7 +2812,7 @@
     <col min="26" max="26" width="69.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="91.3359375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="139.8515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
